--- a/analysis/paper tables and figures/figure 7 self-reported usability feedback.xlsx
+++ b/analysis/paper tables and figures/figure 7 self-reported usability feedback.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\misc\GitHub\FuzzDojo\analysis\paper tables and figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SW\Desktop\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="23263" windowHeight="12463" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Survey-data" sheetId="9" r:id="rId1"/>
@@ -210,9 +210,6 @@
     <t>DOCUMENTATION MISSING/INSUFFICIENT (F17)</t>
   </si>
   <si>
-    <t>Address by fuzz dojo</t>
-  </si>
-  <si>
     <t>Controlled by study</t>
   </si>
   <si>
@@ -394,6 +391,9 @@
   </si>
   <si>
     <t>Always+Often</t>
+  </si>
+  <si>
+    <t>Address by fuzz platform</t>
   </si>
 </sst>
 </file>
@@ -1698,11 +1698,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="537210904"/>
-        <c:axId val="541343736"/>
+        <c:axId val="662583592"/>
+        <c:axId val="662585160"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="537210904"/>
+        <c:axId val="662583592"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1745,7 +1745,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541343736"/>
+        <c:crossAx val="662585160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1753,7 +1753,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="541343736"/>
+        <c:axId val="662585160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1804,7 +1804,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="537210904"/>
+        <c:crossAx val="662583592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2436,13 +2436,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>257174</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2735,12 +2735,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T949"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="12.45"/>
   <cols>
-    <col min="1" max="1" width="14.36328125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" style="1" customWidth="1"/>
-    <col min="3" max="16" width="8.81640625" style="1"/>
-    <col min="17" max="17" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.3828125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="9.84375" style="1" customWidth="1"/>
+    <col min="3" max="16" width="8.84375" style="1"/>
+    <col min="17" max="17" width="10.84375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2760,7 +2760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="409.6" hidden="1" thickBot="1">
+    <row r="4" spans="1:16" ht="385.75" hidden="1" thickBot="1">
       <c r="A4" s="8"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2808,7 +2808,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="63" thickBot="1">
+    <row r="5" spans="1:16" ht="62.6" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
@@ -2858,1076 +2858,1076 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="13" thickBot="1">
+    <row r="6" spans="1:16" ht="12.9" thickBot="1">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
         <v>62</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
         <v>62</v>
       </c>
-      <c r="D6" t="s">
+      <c r="J6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" t="s">
         <v>62</v>
       </c>
-      <c r="E6" t="s">
+      <c r="M6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" t="s">
         <v>63</v>
       </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="P6" t="s">
         <v>63</v>
       </c>
-      <c r="J6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" t="s">
-        <v>63</v>
-      </c>
-      <c r="M6" t="s">
-        <v>63</v>
-      </c>
-      <c r="N6" t="s">
-        <v>63</v>
-      </c>
-      <c r="O6" t="s">
-        <v>64</v>
-      </c>
-      <c r="P6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="7" spans="1:16" ht="12.9" thickBot="1">
       <c r="A7" s="4">
         <f>A6+1</f>
         <v>2</v>
       </c>
       <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" t="s">
         <v>62</v>
       </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
         <v>64</v>
       </c>
-      <c r="E7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" t="s">
         <v>63</v>
       </c>
-      <c r="G7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" t="s">
-        <v>62</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
+        <v>61</v>
+      </c>
+      <c r="N7" t="s">
         <v>64</v>
       </c>
-      <c r="M7" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" t="s">
-        <v>65</v>
-      </c>
       <c r="O7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="13" thickBot="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="12.9" thickBot="1">
       <c r="A8" s="4">
         <f t="shared" ref="A8:A25" si="0">A7+1</f>
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" t="s">
         <v>63</v>
       </c>
-      <c r="C8" t="s">
+      <c r="M8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P8" t="s">
         <v>62</v>
       </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" t="s">
-        <v>62</v>
-      </c>
-      <c r="L8" t="s">
-        <v>64</v>
-      </c>
-      <c r="M8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" t="s">
-        <v>62</v>
-      </c>
-      <c r="O8" t="s">
-        <v>62</v>
-      </c>
-      <c r="P8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="9" spans="1:16" ht="12.9" thickBot="1">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" t="s">
         <v>62</v>
       </c>
-      <c r="G9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" t="s">
         <v>65</v>
       </c>
-      <c r="M9" t="s">
-        <v>63</v>
-      </c>
-      <c r="N9" t="s">
-        <v>65</v>
-      </c>
-      <c r="O9" t="s">
-        <v>66</v>
-      </c>
       <c r="P9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="13" thickBot="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="12.9" thickBot="1">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
         <v>62</v>
       </c>
-      <c r="C10" t="s">
+      <c r="K10" t="s">
         <v>62</v>
       </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" t="s">
-        <v>63</v>
-      </c>
       <c r="L10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="13" thickBot="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="12.9" thickBot="1">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" t="s">
         <v>62</v>
       </c>
-      <c r="C11" t="s">
+      <c r="M11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" t="s">
+        <v>61</v>
+      </c>
+      <c r="O11" t="s">
         <v>62</v>
       </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" t="s">
-        <v>62</v>
-      </c>
-      <c r="J11" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11" t="s">
-        <v>63</v>
-      </c>
-      <c r="M11" t="s">
-        <v>67</v>
-      </c>
-      <c r="N11" t="s">
-        <v>62</v>
-      </c>
-      <c r="O11" t="s">
-        <v>63</v>
-      </c>
       <c r="P11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="13" thickBot="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="12.9" thickBot="1">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
         <v>63</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" t="s">
-        <v>64</v>
-      </c>
       <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="J12" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>63</v>
       </c>
-      <c r="M12" t="s">
-        <v>64</v>
-      </c>
       <c r="N12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="13" thickBot="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="12.9" thickBot="1">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
         <v>64</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
         <v>66</v>
       </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" t="s">
-        <v>67</v>
-      </c>
       <c r="I13" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13" t="s">
         <v>63</v>
       </c>
-      <c r="J13" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>64</v>
       </c>
-      <c r="L13" t="s">
-        <v>65</v>
-      </c>
       <c r="M13" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" t="s">
+        <v>64</v>
+      </c>
+      <c r="O13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P13" t="s">
         <v>63</v>
       </c>
-      <c r="N13" t="s">
-        <v>65</v>
-      </c>
-      <c r="O13" t="s">
-        <v>67</v>
-      </c>
-      <c r="P13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="14" spans="1:16" ht="12.9" thickBot="1">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" t="s">
+        <v>63</v>
+      </c>
+      <c r="K14" t="s">
         <v>62</v>
       </c>
-      <c r="C14" t="s">
+      <c r="L14" t="s">
         <v>62</v>
       </c>
-      <c r="D14" t="s">
+      <c r="M14" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" t="s">
         <v>64</v>
       </c>
-      <c r="E14" t="s">
+      <c r="P14" t="s">
         <v>64</v>
       </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" t="s">
-        <v>64</v>
-      </c>
-      <c r="K14" t="s">
-        <v>63</v>
-      </c>
-      <c r="L14" t="s">
-        <v>63</v>
-      </c>
-      <c r="M14" t="s">
-        <v>63</v>
-      </c>
-      <c r="N14" t="s">
-        <v>62</v>
-      </c>
-      <c r="O14" t="s">
-        <v>65</v>
-      </c>
-      <c r="P14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="15" spans="1:16" ht="12.9" thickBot="1">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
         <v>63</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" t="s">
         <v>65</v>
       </c>
-      <c r="D15" t="s">
+      <c r="H15" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" t="s">
         <v>64</v>
       </c>
-      <c r="E15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="K15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" t="s">
         <v>62</v>
       </c>
-      <c r="G15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="M15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" t="s">
         <v>64</v>
       </c>
-      <c r="I15" t="s">
+      <c r="O15" t="s">
         <v>64</v>
       </c>
-      <c r="J15" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" t="s">
-        <v>64</v>
-      </c>
-      <c r="L15" t="s">
-        <v>63</v>
-      </c>
-      <c r="M15" t="s">
+      <c r="P15" t="s">
         <v>62</v>
       </c>
-      <c r="N15" t="s">
-        <v>65</v>
-      </c>
-      <c r="O15" t="s">
-        <v>65</v>
-      </c>
-      <c r="P15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="16" spans="1:16" ht="12.9" thickBot="1">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
         <v>62</v>
       </c>
-      <c r="C16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="H16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16" t="s">
+        <v>63</v>
+      </c>
+      <c r="P16" t="s">
         <v>64</v>
       </c>
-      <c r="E16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" t="s">
-        <v>62</v>
-      </c>
-      <c r="K16" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N16" t="s">
-        <v>62</v>
-      </c>
-      <c r="O16" t="s">
-        <v>64</v>
-      </c>
-      <c r="P16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="17" spans="1:16" ht="12.9" thickBot="1">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
         <v>66</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17" t="s">
+        <v>65</v>
+      </c>
+      <c r="K17" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17" t="s">
         <v>66</v>
       </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="N17" t="s">
         <v>65</v>
       </c>
-      <c r="H17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" t="s">
-        <v>63</v>
-      </c>
-      <c r="J17" t="s">
-        <v>66</v>
-      </c>
-      <c r="K17" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" t="s">
-        <v>64</v>
-      </c>
-      <c r="M17" t="s">
-        <v>67</v>
-      </c>
-      <c r="N17" t="s">
-        <v>66</v>
-      </c>
       <c r="O17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="13" thickBot="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="12.9" thickBot="1">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
         <v>62</v>
       </c>
-      <c r="C18" t="s">
+      <c r="H18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" t="s">
         <v>62</v>
       </c>
-      <c r="D18" t="s">
+      <c r="K18" t="s">
         <v>62</v>
       </c>
-      <c r="E18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="L18" t="s">
         <v>63</v>
       </c>
-      <c r="H18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" t="s">
-        <v>62</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="M18" t="s">
+        <v>66</v>
+      </c>
+      <c r="N18" t="s">
         <v>63</v>
       </c>
-      <c r="K18" t="s">
-        <v>63</v>
-      </c>
-      <c r="L18" t="s">
-        <v>64</v>
-      </c>
-      <c r="M18" t="s">
-        <v>67</v>
-      </c>
-      <c r="N18" t="s">
-        <v>64</v>
-      </c>
       <c r="O18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="13" thickBot="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="12.9" thickBot="1">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" t="s">
         <v>64</v>
       </c>
-      <c r="D19" t="s">
+      <c r="K19" t="s">
         <v>64</v>
       </c>
-      <c r="E19" t="s">
+      <c r="L19" t="s">
         <v>64</v>
       </c>
-      <c r="F19" t="s">
+      <c r="M19" t="s">
         <v>64</v>
       </c>
-      <c r="G19" t="s">
+      <c r="N19" t="s">
         <v>64</v>
       </c>
-      <c r="H19" t="s">
+      <c r="O19" t="s">
         <v>64</v>
       </c>
-      <c r="I19" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" t="s">
-        <v>65</v>
-      </c>
-      <c r="K19" t="s">
-        <v>65</v>
-      </c>
-      <c r="L19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M19" t="s">
-        <v>65</v>
-      </c>
-      <c r="N19" t="s">
-        <v>65</v>
-      </c>
-      <c r="O19" t="s">
-        <v>65</v>
-      </c>
       <c r="P19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="13" thickBot="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="12.9" thickBot="1">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20" t="s">
         <v>62</v>
       </c>
-      <c r="C20" t="s">
+      <c r="L20" t="s">
         <v>62</v>
       </c>
-      <c r="D20" t="s">
+      <c r="M20" t="s">
+        <v>63</v>
+      </c>
+      <c r="N20" t="s">
+        <v>61</v>
+      </c>
+      <c r="O20" t="s">
+        <v>63</v>
+      </c>
+      <c r="P20" t="s">
         <v>64</v>
       </c>
-      <c r="E20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" t="s">
-        <v>65</v>
-      </c>
-      <c r="K20" t="s">
-        <v>63</v>
-      </c>
-      <c r="L20" t="s">
-        <v>63</v>
-      </c>
-      <c r="M20" t="s">
-        <v>64</v>
-      </c>
-      <c r="N20" t="s">
-        <v>62</v>
-      </c>
-      <c r="O20" t="s">
-        <v>64</v>
-      </c>
-      <c r="P20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="21" spans="1:16" ht="12.9" thickBot="1">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" t="s">
+        <v>64</v>
+      </c>
+      <c r="L21" t="s">
         <v>62</v>
       </c>
-      <c r="C21" t="s">
+      <c r="M21" t="s">
         <v>62</v>
       </c>
-      <c r="D21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" t="s">
-        <v>62</v>
-      </c>
-      <c r="K21" t="s">
-        <v>65</v>
-      </c>
-      <c r="L21" t="s">
-        <v>63</v>
-      </c>
-      <c r="M21" t="s">
-        <v>63</v>
-      </c>
       <c r="N21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="13" thickBot="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="12.9" thickBot="1">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
         <v>63</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" t="s">
         <v>64</v>
       </c>
-      <c r="D22" t="s">
+      <c r="H22" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22" t="s">
         <v>64</v>
       </c>
-      <c r="E22" t="s">
+      <c r="K22" t="s">
+        <v>63</v>
+      </c>
+      <c r="L22" t="s">
         <v>64</v>
       </c>
-      <c r="F22" t="s">
+      <c r="M22" t="s">
+        <v>63</v>
+      </c>
+      <c r="N22" t="s">
         <v>64</v>
       </c>
-      <c r="G22" t="s">
-        <v>65</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="O22" t="s">
+        <v>63</v>
+      </c>
+      <c r="P22" t="s">
         <v>64</v>
       </c>
-      <c r="I22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" t="s">
-        <v>65</v>
-      </c>
-      <c r="K22" t="s">
-        <v>64</v>
-      </c>
-      <c r="L22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22" t="s">
-        <v>64</v>
-      </c>
-      <c r="N22" t="s">
-        <v>65</v>
-      </c>
-      <c r="O22" t="s">
-        <v>64</v>
-      </c>
-      <c r="P22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="23" spans="1:16" ht="12.9" thickBot="1">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" t="s">
         <v>63</v>
       </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J23" t="s">
+        <v>62</v>
+      </c>
+      <c r="K23" t="s">
+        <v>63</v>
+      </c>
+      <c r="L23" t="s">
         <v>64</v>
       </c>
-      <c r="F23" t="s">
+      <c r="M23" t="s">
         <v>62</v>
       </c>
-      <c r="G23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" t="s">
-        <v>62</v>
-      </c>
-      <c r="I23" t="s">
-        <v>62</v>
-      </c>
-      <c r="J23" t="s">
-        <v>63</v>
-      </c>
-      <c r="K23" t="s">
-        <v>64</v>
-      </c>
-      <c r="L23" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" t="s">
-        <v>63</v>
-      </c>
       <c r="N23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="13" thickBot="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="12.9" thickBot="1">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" t="s">
         <v>64</v>
       </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="H24" t="s">
+        <v>65</v>
+      </c>
+      <c r="I24" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" t="s">
+        <v>62</v>
+      </c>
+      <c r="K24" t="s">
         <v>63</v>
       </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" t="s">
-        <v>65</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="L24" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" t="s">
+        <v>61</v>
+      </c>
+      <c r="N24" t="s">
         <v>66</v>
       </c>
-      <c r="I24" t="s">
+      <c r="O24" t="s">
         <v>62</v>
       </c>
-      <c r="J24" t="s">
+      <c r="P24" t="s">
         <v>63</v>
       </c>
-      <c r="K24" t="s">
-        <v>64</v>
-      </c>
-      <c r="L24" t="s">
-        <v>62</v>
-      </c>
-      <c r="M24" t="s">
-        <v>62</v>
-      </c>
-      <c r="N24" t="s">
-        <v>67</v>
-      </c>
-      <c r="O24" t="s">
-        <v>63</v>
-      </c>
-      <c r="P24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="25" spans="1:16" ht="12.9" thickBot="1">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
         <v>62</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>62</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" t="s">
         <v>63</v>
       </c>
-      <c r="E25" t="s">
+      <c r="H25" t="s">
+        <v>61</v>
+      </c>
+      <c r="I25" t="s">
+        <v>61</v>
+      </c>
+      <c r="J25" t="s">
         <v>63</v>
       </c>
-      <c r="F25" t="s">
+      <c r="K25" t="s">
         <v>63</v>
       </c>
-      <c r="G25" t="s">
+      <c r="L25" t="s">
         <v>64</v>
       </c>
-      <c r="H25" t="s">
+      <c r="M25" t="s">
+        <v>64</v>
+      </c>
+      <c r="N25" t="s">
+        <v>63</v>
+      </c>
+      <c r="O25" t="s">
+        <v>64</v>
+      </c>
+      <c r="P25" t="s">
         <v>62</v>
       </c>
-      <c r="I25" t="s">
-        <v>62</v>
-      </c>
-      <c r="J25" t="s">
-        <v>64</v>
-      </c>
-      <c r="K25" t="s">
-        <v>64</v>
-      </c>
-      <c r="L25" t="s">
-        <v>65</v>
-      </c>
-      <c r="M25" t="s">
-        <v>65</v>
-      </c>
-      <c r="N25" t="s">
-        <v>64</v>
-      </c>
-      <c r="O25" t="s">
-        <v>65</v>
-      </c>
-      <c r="P25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="26" spans="1:16" ht="12.9" thickBot="1">
       <c r="A26" s="4">
         <v>21</v>
       </c>
       <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G26" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K26" t="s">
         <v>62</v>
       </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="L26" t="s">
         <v>64</v>
       </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" t="s">
-        <v>62</v>
-      </c>
-      <c r="I26" t="s">
-        <v>62</v>
-      </c>
-      <c r="J26" t="s">
-        <v>62</v>
-      </c>
-      <c r="K26" t="s">
+      <c r="M26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" t="s">
+        <v>61</v>
+      </c>
+      <c r="O26" t="s">
+        <v>66</v>
+      </c>
+      <c r="P26" t="s">
         <v>63</v>
       </c>
-      <c r="L26" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" t="s">
-        <v>62</v>
-      </c>
-      <c r="N26" t="s">
-        <v>62</v>
-      </c>
-      <c r="O26" t="s">
-        <v>67</v>
-      </c>
-      <c r="P26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="13" thickBot="1">
+    </row>
+    <row r="27" spans="1:16" ht="12.9" thickBot="1">
       <c r="A27" s="4"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -4665,26 +4665,26 @@
       <c r="I45" s="20"/>
       <c r="J45" s="20"/>
       <c r="L45" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N45" s="20"/>
       <c r="O45" s="20"/>
       <c r="P45" s="20"/>
       <c r="Q45" s="21"/>
       <c r="R45" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="S45" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="S45" s="21" t="s">
+      <c r="T45" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="T45" s="21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" ht="14.5">
+    </row>
+    <row r="46" spans="1:20" ht="14.6">
       <c r="A46" s="32"/>
       <c r="B46" s="33"/>
       <c r="C46" s="20"/>
@@ -4696,10 +4696,10 @@
       <c r="I46" s="20"/>
       <c r="J46" s="20"/>
       <c r="L46" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M46" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N46" s="30"/>
       <c r="O46" s="30"/>
@@ -4716,7 +4716,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="14.5">
+    <row r="47" spans="1:20" ht="14.6">
       <c r="A47" s="32"/>
       <c r="B47" s="33"/>
       <c r="C47" s="20"/>
@@ -4728,10 +4728,10 @@
       <c r="I47" s="20"/>
       <c r="J47" s="20"/>
       <c r="L47" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M47" s="25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N47" s="26"/>
       <c r="O47" s="26"/>
@@ -4748,7 +4748,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="14.5">
+    <row r="48" spans="1:20" ht="14.6">
       <c r="A48" s="32"/>
       <c r="B48" s="33"/>
       <c r="C48" s="20"/>
@@ -4760,10 +4760,10 @@
       <c r="I48" s="20"/>
       <c r="J48" s="20"/>
       <c r="L48" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M48" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N48" s="30"/>
       <c r="O48" s="30"/>
@@ -4780,7 +4780,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="14.5">
+    <row r="49" spans="1:20" ht="14.6">
       <c r="A49" s="32"/>
       <c r="B49" s="33"/>
       <c r="C49" s="20"/>
@@ -4792,10 +4792,10 @@
       <c r="I49" s="20"/>
       <c r="J49" s="20"/>
       <c r="L49" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M49" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N49" s="26"/>
       <c r="O49" s="26"/>
@@ -4812,7 +4812,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="14.5">
+    <row r="50" spans="1:20" ht="14.6">
       <c r="A50" s="32"/>
       <c r="B50" s="33"/>
       <c r="C50" s="20"/>
@@ -4824,10 +4824,10 @@
       <c r="I50" s="20"/>
       <c r="J50" s="20"/>
       <c r="L50" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M50" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N50" s="26"/>
       <c r="O50" s="26"/>
@@ -4844,7 +4844,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="14.5">
+    <row r="51" spans="1:20" ht="14.6">
       <c r="A51" s="32"/>
       <c r="B51" s="33"/>
       <c r="C51" s="20"/>
@@ -4856,10 +4856,10 @@
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
       <c r="L51" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M51" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N51" s="19"/>
       <c r="O51" s="19"/>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="14.5">
+    <row r="52" spans="1:20" ht="14.6">
       <c r="A52" s="32"/>
       <c r="B52" s="33"/>
       <c r="C52" s="20"/>
@@ -4888,10 +4888,10 @@
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
       <c r="L52" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M52" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N52" s="26"/>
       <c r="O52" s="26"/>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="14.5">
+    <row r="53" spans="1:20" ht="14.6">
       <c r="A53" s="32"/>
       <c r="B53" s="33"/>
       <c r="C53" s="20"/>
@@ -4920,10 +4920,10 @@
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
       <c r="L53" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M53" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N53" s="19"/>
       <c r="O53" s="19"/>
@@ -4940,7 +4940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="14.5">
+    <row r="54" spans="1:20" ht="14.6">
       <c r="A54" s="32"/>
       <c r="B54" s="33"/>
       <c r="C54" s="20"/>
@@ -4952,10 +4952,10 @@
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
       <c r="L54" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M54" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N54" s="26"/>
       <c r="O54" s="26"/>
@@ -4972,7 +4972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="14.5">
+    <row r="55" spans="1:20" ht="14.6">
       <c r="A55" s="32"/>
       <c r="B55" s="33"/>
       <c r="C55" s="20"/>
@@ -4984,10 +4984,10 @@
       <c r="I55" s="20"/>
       <c r="J55" s="20"/>
       <c r="L55" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M55" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N55" s="30"/>
       <c r="O55" s="30"/>
@@ -5004,7 +5004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="14.5">
+    <row r="56" spans="1:20" ht="14.6">
       <c r="A56" s="32"/>
       <c r="B56" s="33"/>
       <c r="C56" s="20"/>
@@ -5016,10 +5016,10 @@
       <c r="I56" s="20"/>
       <c r="J56" s="20"/>
       <c r="L56" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M56" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N56" s="26"/>
       <c r="O56" s="26"/>
@@ -5036,7 +5036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="14.5">
+    <row r="57" spans="1:20" ht="14.6">
       <c r="A57" s="32"/>
       <c r="B57" s="33"/>
       <c r="C57" s="20"/>
@@ -5048,10 +5048,10 @@
       <c r="I57" s="20"/>
       <c r="J57" s="20"/>
       <c r="L57" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M57" s="27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N57" s="26"/>
       <c r="O57" s="26"/>
@@ -5068,7 +5068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="14.5">
+    <row r="58" spans="1:20" ht="14.6">
       <c r="A58" s="32"/>
       <c r="B58" s="33"/>
       <c r="C58" s="20"/>
@@ -5080,10 +5080,10 @@
       <c r="I58" s="20"/>
       <c r="J58" s="20"/>
       <c r="L58" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M58" s="28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N58" s="19"/>
       <c r="O58" s="19"/>
@@ -5100,7 +5100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="14.5">
+    <row r="59" spans="1:20" ht="14.6">
       <c r="A59" s="32"/>
       <c r="B59" s="33"/>
       <c r="C59" s="20"/>
@@ -5112,10 +5112,10 @@
       <c r="I59" s="20"/>
       <c r="J59" s="20"/>
       <c r="L59" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M59" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N59" s="26"/>
       <c r="O59" s="26"/>
@@ -5132,7 +5132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="14.5">
+    <row r="60" spans="1:20" ht="14.6">
       <c r="A60" s="32"/>
       <c r="B60" s="33"/>
       <c r="C60" s="20"/>
@@ -5144,10 +5144,10 @@
       <c r="I60" s="20"/>
       <c r="J60" s="20"/>
       <c r="L60" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M60" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N60" s="19"/>
       <c r="O60" s="19"/>
@@ -5183,11 +5183,11 @@
       <c r="B66" s="11"/>
       <c r="D66" s="18"/>
     </row>
-    <row r="67" spans="2:10" ht="14.5">
+    <row r="67" spans="2:10" ht="14.6">
       <c r="B67" s="11"/>
       <c r="J67" s="19"/>
     </row>
-    <row r="68" spans="2:10" ht="14.5">
+    <row r="68" spans="2:10" ht="14.6">
       <c r="B68" s="11"/>
       <c r="J68" s="19"/>
     </row>
@@ -7845,15 +7845,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T66"/>
-  <sheetFormatPr defaultRowHeight="14" customHeight="1"/>
+  <dimension ref="A1:T64"/>
+  <sheetFormatPr defaultRowHeight="14.05" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="61.90625" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" customWidth="1"/>
+    <col min="2" max="2" width="61.921875" customWidth="1"/>
+    <col min="10" max="10" width="14.4609375" customWidth="1"/>
+    <col min="12" max="12" width="8.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="14" customHeight="1">
+    <row r="1" spans="1:20" ht="14.05" customHeight="1">
       <c r="B1" s="12"/>
       <c r="C1" s="17" t="s">
         <v>42</v>
@@ -7871,13 +7871,13 @@
         <v>38</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L1" s="22"/>
       <c r="M1" s="22"/>
@@ -7889,12 +7889,12 @@
       <c r="S1" s="23"/>
       <c r="T1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="14" customHeight="1">
+    <row r="2" spans="1:20" ht="14.05" customHeight="1">
       <c r="A2">
         <v>22</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -7930,12 +7930,12 @@
       <c r="Q2" s="11"/>
       <c r="T2" s="23"/>
     </row>
-    <row r="3" spans="1:20" ht="14" customHeight="1">
+    <row r="3" spans="1:20" ht="14.05" customHeight="1">
       <c r="A3">
         <v>15</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -7971,12 +7971,12 @@
       <c r="Q3" s="1"/>
       <c r="T3" s="23"/>
     </row>
-    <row r="4" spans="1:20" ht="14" customHeight="1">
+    <row r="4" spans="1:20" ht="14.05" customHeight="1">
       <c r="A4">
         <v>21</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -8012,12 +8012,12 @@
       <c r="Q4" s="1"/>
       <c r="T4" s="23"/>
     </row>
-    <row r="5" spans="1:20" ht="14" customHeight="1">
+    <row r="5" spans="1:20" ht="14.05" customHeight="1">
       <c r="A5">
         <v>20</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -8053,12 +8053,12 @@
       <c r="Q5" s="1"/>
       <c r="T5" s="23"/>
     </row>
-    <row r="6" spans="1:20" ht="14" customHeight="1">
+    <row r="6" spans="1:20" ht="14.05" customHeight="1">
       <c r="A6">
         <v>17</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -8094,12 +8094,12 @@
       <c r="Q6" s="1"/>
       <c r="T6" s="23"/>
     </row>
-    <row r="7" spans="1:20" ht="14" customHeight="1">
+    <row r="7" spans="1:20" ht="14.05" customHeight="1">
       <c r="A7">
         <v>9</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -8135,12 +8135,12 @@
       <c r="Q7" s="1"/>
       <c r="T7" s="23"/>
     </row>
-    <row r="8" spans="1:20" ht="14" customHeight="1">
+    <row r="8" spans="1:20" ht="14.05" customHeight="1">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -8176,12 +8176,12 @@
       <c r="Q8" s="1"/>
       <c r="T8" s="23"/>
     </row>
-    <row r="9" spans="1:20" ht="14" customHeight="1">
+    <row r="9" spans="1:20" ht="14.05" customHeight="1">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
@@ -8217,12 +8217,12 @@
       <c r="Q9" s="1"/>
       <c r="T9" s="23"/>
     </row>
-    <row r="10" spans="1:20" ht="14" customHeight="1">
+    <row r="10" spans="1:20" ht="14.05" customHeight="1">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
@@ -8258,12 +8258,12 @@
       <c r="Q10" s="1"/>
       <c r="T10" s="23"/>
     </row>
-    <row r="11" spans="1:20" ht="14" customHeight="1">
+    <row r="11" spans="1:20" ht="14.05" customHeight="1">
       <c r="A11">
         <v>16</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11" s="1">
         <v>2</v>
@@ -8299,12 +8299,12 @@
       <c r="Q11" s="1"/>
       <c r="T11" s="23"/>
     </row>
-    <row r="12" spans="1:20" ht="14" customHeight="1">
+    <row r="12" spans="1:20" ht="14.05" customHeight="1">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
@@ -8340,12 +8340,12 @@
       <c r="Q12" s="1"/>
       <c r="T12" s="23"/>
     </row>
-    <row r="13" spans="1:20" ht="14" customHeight="1">
+    <row r="13" spans="1:20" ht="14.05" customHeight="1">
       <c r="A13">
         <v>8</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
@@ -8381,12 +8381,12 @@
       <c r="Q13" s="1"/>
       <c r="T13" s="23"/>
     </row>
-    <row r="14" spans="1:20" ht="14" customHeight="1">
+    <row r="14" spans="1:20" ht="14.05" customHeight="1">
       <c r="A14">
         <v>18</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
@@ -8422,12 +8422,12 @@
       <c r="Q14" s="1"/>
       <c r="T14" s="23"/>
     </row>
-    <row r="15" spans="1:20" ht="14" customHeight="1">
+    <row r="15" spans="1:20" ht="14.05" customHeight="1">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="11">
         <v>1</v>
@@ -8463,12 +8463,12 @@
       <c r="Q15" s="1"/>
       <c r="T15" s="23"/>
     </row>
-    <row r="16" spans="1:20" ht="14" customHeight="1">
+    <row r="16" spans="1:20" ht="14.05" customHeight="1">
       <c r="A16">
         <v>11</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
@@ -8504,403 +8504,403 @@
       <c r="Q16" s="1"/>
       <c r="T16" s="23"/>
     </row>
-    <row r="23" spans="2:2" ht="14" customHeight="1">
-      <c r="B23" s="14" t="s">
+    <row r="21" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B21" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B22" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B23" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B24" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B25" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B26" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B27" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B28" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B29" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B30" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B38" s="14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="14" customHeight="1">
-      <c r="B24" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" ht="14" customHeight="1">
-      <c r="B25" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" ht="14" customHeight="1">
-      <c r="B26" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" ht="14" customHeight="1">
-      <c r="B27" s="13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" ht="14" customHeight="1">
-      <c r="B28" s="13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" ht="14" customHeight="1">
-      <c r="B29" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" ht="14" customHeight="1">
-      <c r="B30" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" ht="14" customHeight="1">
-      <c r="B31" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" ht="14" customHeight="1">
-      <c r="B32" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="14" customHeight="1">
-      <c r="B40" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" ht="14" customHeight="1">
+    <row r="39" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B39" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" ht="14.05" customHeight="1">
+      <c r="B40" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" ht="14.05" customHeight="1">
       <c r="B41" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" ht="14" customHeight="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" ht="14.05" customHeight="1">
       <c r="B42" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" ht="14" customHeight="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" ht="14.05" customHeight="1">
       <c r="B43" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" ht="14" customHeight="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" ht="14.05" customHeight="1">
       <c r="B44" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" ht="14" customHeight="1">
-      <c r="B45" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" ht="14" customHeight="1">
-      <c r="B46" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="5:11" ht="14" customHeight="1">
-      <c r="E52" s="11"/>
-      <c r="F52" s="11">
+    <row r="50" spans="5:11" ht="14.05" customHeight="1">
+      <c r="E50" s="11"/>
+      <c r="F50" s="11">
         <v>1</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G50" s="11">
         <v>0</v>
       </c>
-      <c r="H52" s="11">
-        <v>2</v>
-      </c>
-      <c r="I52" s="11">
+      <c r="H50" s="11">
+        <v>2</v>
+      </c>
+      <c r="I50" s="11">
         <v>6</v>
       </c>
-      <c r="J52" s="11">
+      <c r="J50" s="11">
         <v>10</v>
       </c>
-      <c r="K52" s="11">
+      <c r="K50" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="5:11" ht="14" customHeight="1">
+    <row r="51" spans="5:11" ht="14.05" customHeight="1">
+      <c r="E51" s="1"/>
+      <c r="F51" s="1">
+        <v>2</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="1">
+        <v>3</v>
+      </c>
+      <c r="I51" s="1">
+        <v>2</v>
+      </c>
+      <c r="J51" s="1">
+        <v>11</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="5:11" ht="14.05" customHeight="1">
+      <c r="E52" s="1"/>
+      <c r="F52" s="1">
+        <v>2</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="1">
+        <v>12</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="J52" s="1">
+        <v>3</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="5:11" ht="14.05" customHeight="1">
       <c r="E53" s="1"/>
       <c r="F53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="1">
+        <v>7</v>
+      </c>
+      <c r="I53" s="1">
         <v>3</v>
       </c>
-      <c r="I53" s="1">
-        <v>2</v>
-      </c>
       <c r="J53" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="5:11" ht="14" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="5:11" ht="14.05" customHeight="1">
       <c r="E54" s="1"/>
       <c r="F54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I54" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="5:11" ht="14" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="5:11" ht="14.05" customHeight="1">
       <c r="E55" s="1"/>
       <c r="F55" s="1">
         <v>1</v>
       </c>
       <c r="G55" s="1">
+        <v>5</v>
+      </c>
+      <c r="H55" s="1">
         <v>4</v>
       </c>
-      <c r="H55" s="1">
-        <v>7</v>
-      </c>
       <c r="I55" s="1">
+        <v>2</v>
+      </c>
+      <c r="J55" s="1">
+        <v>5</v>
+      </c>
+      <c r="K55" s="1">
         <v>3</v>
       </c>
-      <c r="J55" s="1">
-        <v>3</v>
-      </c>
-      <c r="K55" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="5:11" ht="14" customHeight="1">
+    </row>
+    <row r="56" spans="5:11" ht="14.05" customHeight="1">
       <c r="E56" s="1"/>
       <c r="F56" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="1">
         <v>5</v>
       </c>
       <c r="I56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K56" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="5:11" ht="14" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="5:11" ht="14.05" customHeight="1">
       <c r="E57" s="1"/>
       <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
         <v>1</v>
       </c>
-      <c r="G57" s="1">
-        <v>5</v>
-      </c>
       <c r="H57" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K57" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="5:11" ht="14" customHeight="1">
+    <row r="58" spans="5:11" ht="14.05" customHeight="1">
       <c r="E58" s="1"/>
       <c r="F58" s="1">
         <v>2</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H58" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I58" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J58" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K58" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="5:11" ht="14" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="5:11" ht="14.05" customHeight="1">
       <c r="E59" s="1"/>
       <c r="F59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="1">
+        <v>2</v>
+      </c>
+      <c r="H59" s="1">
+        <v>7</v>
+      </c>
+      <c r="I59" s="1">
+        <v>4</v>
+      </c>
+      <c r="J59" s="1">
+        <v>4</v>
+      </c>
+      <c r="K59" s="1">
         <v>1</v>
       </c>
-      <c r="H59" s="1">
-        <v>2</v>
-      </c>
-      <c r="I59" s="1">
-        <v>3</v>
-      </c>
-      <c r="J59" s="1">
-        <v>11</v>
-      </c>
-      <c r="K59" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="5:11" ht="14" customHeight="1">
+    </row>
+    <row r="60" spans="5:11" ht="14.05" customHeight="1">
       <c r="E60" s="1"/>
       <c r="F60" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H60" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J60" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K60" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="5:11" ht="14" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="5:11" ht="14.05" customHeight="1">
       <c r="E61" s="1"/>
       <c r="F61" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" s="1">
         <v>2</v>
       </c>
       <c r="H61" s="1">
+        <v>3</v>
+      </c>
+      <c r="I61" s="1">
         <v>7</v>
       </c>
-      <c r="I61" s="1">
-        <v>4</v>
-      </c>
       <c r="J61" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="5:11" ht="14" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="5:11" ht="14.05" customHeight="1">
       <c r="E62" s="1"/>
       <c r="F62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="1">
         <v>6</v>
       </c>
       <c r="H62" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I62" s="1">
+        <v>2</v>
+      </c>
+      <c r="J62" s="1">
         <v>7</v>
       </c>
-      <c r="J62" s="1">
-        <v>2</v>
-      </c>
       <c r="K62" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="5:11" ht="14" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="5:11" ht="14.05" customHeight="1">
       <c r="E63" s="1"/>
       <c r="F63" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H63" s="1">
+        <v>4</v>
+      </c>
+      <c r="I63" s="1">
         <v>3</v>
       </c>
-      <c r="I63" s="1">
-        <v>7</v>
-      </c>
       <c r="J63" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K63" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="5:11" ht="14" customHeight="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="5:11" ht="14.05" customHeight="1">
       <c r="E64" s="1"/>
       <c r="F64" s="1">
         <v>1</v>
       </c>
       <c r="G64" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H64" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I64" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J64" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K64" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="5:11" ht="14" customHeight="1">
-      <c r="E65" s="1"/>
-      <c r="F65" s="1">
-        <v>2</v>
-      </c>
-      <c r="G65" s="1">
-        <v>5</v>
-      </c>
-      <c r="H65" s="1">
-        <v>4</v>
-      </c>
-      <c r="I65" s="1">
-        <v>3</v>
-      </c>
-      <c r="J65" s="1">
-        <v>2</v>
-      </c>
-      <c r="K65" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="5:11" ht="14" customHeight="1">
-      <c r="E66" s="1"/>
-      <c r="F66" s="1">
-        <v>1</v>
-      </c>
-      <c r="G66" s="1">
-        <v>7</v>
-      </c>
-      <c r="H66" s="1">
-        <v>3</v>
-      </c>
-      <c r="I66" s="1">
-        <v>4</v>
-      </c>
-      <c r="J66" s="1">
-        <v>2</v>
-      </c>
-      <c r="K66" s="1">
         <v>3</v>
       </c>
     </row>
